--- a/diccionario_equivalencias.xlsx
+++ b/diccionario_equivalencias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B222"/>
+  <dimension ref="A1:B228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,1975 +899,1975 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ROSUVINA 10/40</t>
+          <t>ROSUVINA 10MG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EZETIMIBA+ROSUVASTATINA 10MG+40MG TAB CX30 (ROSUVINA E) - LEGRAND</t>
+          <t>ROSUVASTATINA 10MG TAB CX30 (ROSUVINA) - LEGRAND</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ROSUVINA 10/40</t>
+          <t>ROSUVINA 20MG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EZETIMIBA+ROSUVASTATINA10MG+40MG TAB CX28 (ROSUVINA E) - LEGRAND</t>
+          <t>ROSUVASTATINA 20MG TAB CX30 (ROSUVINA) - LEGRAND</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ROSUVINA 10MG</t>
+          <t>ROSUVINA 40MG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ROSUVASTATINA 10MG TAB CX30 (ROSUVINA) - LEGRAND</t>
+          <t>ROSUVASTATINA 40MG C*30 TAB (ROSUVINA 40) LEGRAND</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ROSUVINA 20MG</t>
+          <t>SYMBICORT TURBUHALER 160/4.5 X60</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ROSUVASTATINA 20MG TAB CX30 (ROSUVINA) - LEGRAND</t>
+          <t>BUDESONIDA+FORMOTEROL FUMARATO 160MCG+4.5MCG INH BUC FCOX60 DOSIS CX1 (SYMBICORT TURBUHALER) - ASTRAZENECA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ROSUVINA 40MG</t>
+          <t>SYMBICORT RAPIHALER 160/4.5 X120</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ROSUVASTATINA 40MG C*30 TAB (ROSUVINA 40) LEGRAND</t>
+          <t>BUDESONIDA+FORMOTEROL FUMARATO 160MCG+4.5MCG SUSP INH BUC C*1 FCO X 120 DOSIS (SYMBICORT RAPIHALER) - ASTRAZENECA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SYMBICORT TURBUHALER 160/4.5 X60</t>
+          <t>SYMBICORT TURBUHALER 320/9 X60</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BUDESONIDA+FORMOTEROL FUMARATO 160MCG+4.5MCG INH BUC FCOX60 DOSIS CX1 (SYMBICORT TURBUHALER) - ASTRAZENECA</t>
+          <t>BUDESONIDE + FORMOTEROL (320+9) MCG(SYMBICORT TURBUHALER) CAJA X 1 INHALADOR X 60 DOSIS INHALADOR ASTRAZENECA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SYMBICORT RAPIHALER 160/4.5 X120</t>
+          <t>SYMBICORT RAPIHALER 80/4.5 X120</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BUDESONIDA+FORMOTEROL FUMARATO 160MCG+4.5MCG SUSP INH BUC C*1 FCO X 120 DOSIS (SYMBICORT RAPIHALER) - ASTRAZENECA</t>
+          <t>BUDESONIDE + FORMOTEROL (80+4.5) MCG  (SYMBICORT RAPIHALER) SUSPENSION PARA NEBULIZAR BUCAL FRASCO X 120 DOSIS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SYMBICORT TURBUHALER 320/9 X60</t>
+          <t>SYMBICORT TURBUHALER 160/4.5 X120</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BUDESONIDE + FORMOTEROL (320+9) MCG(SYMBICORT TURBUHALER) CAJA X 1 INHALADOR X 60 DOSIS INHALADOR ASTRAZENECA</t>
+          <t>BUDESONIDE + FORMOTEROL TURBUHALER  (160+4.5) MCG INHALADOR(SYMBICORT TURBUHALER) FRASCO X 120 DOSIS ASTRAZENECA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SYMBICORT RAPIHALER 80/4.5 X120</t>
+          <t>RISPERDAL 25MG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BUDESONIDE + FORMOTEROL (80+4.5) MCG  (SYMBICORT RAPIHALER) SUSPENSION PARA NEBULIZAR BUCAL FRASCO X 120 DOSIS</t>
+          <t>RISPERIDONA 25MG POL INY VIAL+DIL CX1 (RISPERDAL CONSTA) - JANSSEN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SYMBICORT TURBUHALER 160/4.5 X120</t>
+          <t>RISPERDAL 37.5MG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BUDESONIDE + FORMOTEROL TURBUHALER  (160+4.5) MCG INHALADOR(SYMBICORT TURBUHALER) FRASCO X 120 DOSIS ASTRAZENECA</t>
+          <t>RISPERIDONA 37.5MG POL INY VIAL+DIL CX1 (RISPERDAL CONSTA) - JANSSEN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RISPERDAL 25MG</t>
+          <t>HUMIRA AC 40MG/0.4ML</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RISPERIDONA 25MG POL INY VIAL+DIL CX1 (RISPERDAL CONSTA) - JANSSEN</t>
+          <t>ADALIMUMAB 40MG/0.4ML SOL INY JERPREX0.4ML CX2 (HUMIRA AC) - ABBVIE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RISPERDAL 37.5MG</t>
+          <t>LENVIMA 10MG X30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RISPERIDONA 37.5MG POL INY VIAL+DIL CX1 (RISPERDAL CONSTA) - JANSSEN</t>
+          <t>LENVATINIB 10MG CAP CX30 (LENVIMA) - BIOTOSCANA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HUMIRA AC 40MG/0.4ML</t>
+          <t>LENVIMA 4MG X30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ADALIMUMAB 40MG/0.4ML SOL INY JERPREX0.4ML CX2 (HUMIRA AC) - ABBVIE</t>
+          <t>LENVATINIB 4MG CAP CX30 (LENVIMA) - BIOTOSCANA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LENVIMA 10MG X30</t>
+          <t>OFEV 150MG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LENVATINIB 10MG CAP CX30 (LENVIMA) - BIOTOSCANA</t>
+          <t>NINTEDANIB ESILATO 150 MG CAPSULA BLANDA  CAJA X 60OFEV150mg® ( BOEHRINGER )</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LENVIMA 4MG X30</t>
+          <t>OFEV 100MG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LENVATINIB 4MG CAP CX30 (LENVIMA) - BIOTOSCANA</t>
+          <t>NINTEDANIB ESILATO 100 MG CAPSULA BLANDA   CAJA X 60OFEV 100MG® ( BOEHRINGER )</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OFEV 150MG</t>
+          <t>FORXIGA 10MG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NINTEDANIB ESILATO 150 MG CAPSULA BLANDA  CAJA X 60OFEV150mg® ( BOEHRINGER )</t>
+          <t>DAPAGLIFLOZINA 10MG TAB CX28 (FORXIGA) - ASTRAZENECA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OFEV 100MG</t>
+          <t>JARDIANCE 10MG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NINTEDANIB ESILATO 100 MG CAPSULA BLANDA   CAJA X 60OFEV 100MG® ( BOEHRINGER )</t>
+          <t>EMPAGLIFLOZINA 10MG TAB CX30 (JARDIANCE) - BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FORXIGA 10MG</t>
+          <t>JARDIANCE 25MG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DAPAGLIFLOZINA 10MG TAB CX28 (FORXIGA) - ASTRAZENECA</t>
+          <t>EMPAGLIFLOZINA 25MG TAB CX30 (JARDIANCE) - BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JARDIANCE 10MG</t>
+          <t>JARDIANCE DUO 1000MG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA 10MG TAB CX30 (JARDIANCE) - BOEHRINGER</t>
+          <t>EMPAGLIFLOZINA+METFORMINA 12.5MG+1000MG TAB CX60 (JARDIANCE DUO) - BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JARDIANCE 25MG</t>
+          <t>JARDIANCE DUO 850MG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA 25MG TAB CX30 (JARDIANCE) - BOEHRINGER</t>
+          <t>EMPAGLIFLOZINA+METFORMINA 12.5MG+850MG TAB CX60 (JARDIANCE DUO) - BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JARDIANCE DUO 1000MG</t>
+          <t>TRAYENTA 5MG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA+METFORMINA 12.5MG+1000MG TAB CX60 (JARDIANCE DUO) - BOEHRINGER</t>
+          <t>LINAGLIPTINA 5 MG COMRIMIDOS RECUBIERTO  CAJA X 30TRAYENTA 5MG ( BOEHRINGER )</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JARDIANCE DUO 850MG</t>
+          <t>TRAYENTA DUO 1000MG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA+METFORMINA 12.5MG+850MG TAB CX60 (JARDIANCE DUO) - BOEHRINGER</t>
+          <t>LINAGLIPTINA+METFORMINA2.5MG+1.000MG TAB FCOX60 CX1 (TRAYENTA DUO) - BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TRAYENTA 5MG</t>
+          <t>TRAYENTA DUO 850MG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LINAGLIPTINA 5 MG COMRIMIDOS RECUBIERTO  CAJA X 30TRAYENTA 5MG ( BOEHRINGER )</t>
+          <t>LINAGLIPTINA+METFORMINA2.5MG+850MG TAB FCOX60 CX1 (TRAYENTA DUO) - BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TRAYENTA DUO 1000MG</t>
+          <t>REPATHA 140MG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LINAGLIPTINA+METFORMINA2.5MG+1.000MG TAB FCOX60 CX1 (TRAYENTA DUO) - BOEHRINGER</t>
+          <t>EVOLOCUMAB 140MG/ML SOL INY PENX1ML CX2 (REPATHA) - AMGEN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TRAYENTA DUO 850MG</t>
+          <t>ZYTIGA 500MG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LINAGLIPTINA+METFORMINA2.5MG+850MG TAB FCOX60 CX1 (TRAYENTA DUO) - BOEHRINGER</t>
+          <t>ABIRATERONA 500MG TAB FCOX60 CX1 (ZYTIGA) - JANSSEN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>REPATHA 140MG</t>
+          <t>ALUDEL 40MG X120</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EVOLOCUMAB 140MG/ML SOL INY PENX1ML CX2 (REPATHA) - AMGEN</t>
+          <t>ENZALUTAMIDA 40MG CAP CX120 (ALUDEL) - PROCAPS</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ZYTIGA 500MG</t>
+          <t>EXELON PATCH 15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ABIRATERONA 500MG TAB FCOX60 CX1 (ZYTIGA) - JANSSEN</t>
+          <t>RIVASTIGMINA 27MG SIST TRANSD PARCH CX30 (EXELON 13.3MG/24H) - BIOTOSCANA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ALUDEL 40MG X120</t>
+          <t>EXELON PATCH 10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ENZALUTAMIDA 40MG CAP CX120 (ALUDEL) - PROCAPS</t>
+          <t>RIVASTIGMINA 18 MG (9.5MG/24H) PARCHE TRANSDÉRMICO  CAJA X 30EXELON PATCH 10 ( BIOTOSCANA )</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EXELON PATCH 15</t>
+          <t>EXELON PATCH 5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RIVASTIGMINA 27MG SIST TRANSD PARCH CX30 (EXELON 13.3MG/24H) - BIOTOSCANA</t>
+          <t>RIVASTIGMINA 9MG SIST TRANSD PARCH CX30 (EXELON 4.6MG/24H) - BIOTOSCANA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EXELON PATCH 10</t>
+          <t>TENA CLASIC M</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RIVASTIGMINA 18 MG (9.5MG/24H) PARCHE TRANSDÉRMICO  CAJA X 30EXELON PATCH 10 ( BIOTOSCANA )</t>
+          <t>PAÑAL TENA SLIP CLASICO TALLA (M) PAQ*30 UND - FAMILIA</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EXELON PATCH 5</t>
+          <t>TENA CLASIC L</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RIVASTIGMINA 9MG SIST TRANSD PARCH CX30 (EXELON 4.6MG/24H) - BIOTOSCANA</t>
+          <t>PAÑAL TENA SLIP CLASICO TALLA (L) PAQ* 30 UND - FAMILIA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TENA CLASIC M</t>
+          <t>TENA ULTRA M</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PAÑAL TENA SLIP CLASICO TALLA (M) PAQ*30 UND - FAMILIA</t>
+          <t>PAÑAL  TENA SLIPT ULTRA TALLA (M) PAQ *30 UND- FAMILIA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TENA CLASIC L</t>
+          <t>TENA ULTRA L</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PAÑAL TENA SLIP CLASICO TALLA (L) PAQ* 30 UND - FAMILIA</t>
+          <t>PAÑAL TENA SLIP ULTRA TALLA (L) PAQ*30 - FAMILIA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TENA ULTRA M</t>
+          <t>TENA ULTRA S</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PAÑAL  TENA SLIPT ULTRA TALLA (M) PAQ *30 UND- FAMILIA</t>
+          <t>PAÑAL TENA SLIP ULTRA TALLA (S) PAQ*30 - FAMILIA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TENA ULTRA L</t>
+          <t>TENA ULTRA XL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PAÑAL TENA SLIP ULTRA TALLA (L) PAQ*30 - FAMILIA</t>
+          <t>PAÑAL  TENA SLIP ULTRA TALLA (XL) PAQ*30 UNID- FAMILIA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TENA ULTRA S</t>
+          <t>TENA PANTS M</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PAÑAL TENA SLIP ULTRA TALLA (S) PAQ*30 - FAMILIA</t>
+          <t>PAÑAL PARA ADULTO TENA PANTST (M) PAQUETE X30 UNIDADES</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TENA ULTRA XL</t>
+          <t>TENA PANTS L</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PAÑAL  TENA SLIP ULTRA TALLA (XL) PAQ*30 UNID- FAMILIA</t>
+          <t>PAÑAL TENA PANTS TALLA (L) PAQ* 30 UND- FAMILIA</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TENA PANTS M</t>
+          <t>ZENIBE 10/40</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PAÑAL PARA ADULTO TENA PANTST (M) PAQUETE X30 UNIDADES</t>
+          <t>EZETIMIBA+ROSUVASTATINA 10MG+40MG C*30 TAB (ZENIBE) - SANOFI</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TENA PANTS L</t>
+          <t>HIDRIBET 10% 125ML</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PAÑAL TENA PANTS TALLA (L) PAQ* 30 UND- FAMILIA</t>
+          <t>HIDRATANTE+FILTRO SOLAR LOC TOP C*1 FCO X 125ML (HIDRIBET) - MEGALABS</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ZENIBE 10/40</t>
+          <t>JANUVIA 100MG X28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EZETIMIBA+ROSUVASTATINA 10MG+40MG C*30 TAB (ZENIBE) - SANOFI</t>
+          <t>SITAGLIPTINA (JANUVIA) 100 MG TABLETA RECUBIERTA CAJA X28</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HIDRIBET 10% 125ML</t>
+          <t>JANUVIA 100MG X14</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HIDRATANTE+FILTRO SOLAR LOC TOP C*1 FCO X 125ML (HIDRIBET) - MEGALABS</t>
+          <t>SITAGLIPTINA (JANUVIA)100 MG TABLETA RECUBIERTA CAJA X14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>JANUVIA 100MG X28</t>
+          <t>JANUVIA 50MG X28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SITAGLIPTINA (JANUVIA) 100 MG TABLETA RECUBIERTA CAJA X28</t>
+          <t>SITAGLIPTINA (JANUVIA) 50 MG TABLETA RECUBIERTA CAJA X28</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>JANUVIA 100MG X14</t>
+          <t>JANUVIA 25MG X28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SITAGLIPTINA (JANUVIA)100 MG TABLETA RECUBIERTA CAJA X14</t>
+          <t>SITAGLIPTINA (JANUVIA) 25 MG TABLETA RECUBIERTA CAJA X 28</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>JANUVIA 50MG X28</t>
+          <t>LYRICA 25MG X30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SITAGLIPTINA (JANUVIA) 50 MG TABLETA RECUBIERTA CAJA X28</t>
+          <t>PREGABALINA (LYRICA) 25 MG CAPSULA CAJA X 30 - PFIZER</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>JANUVIA 25MG X28</t>
+          <t>LYRICA 50MG X30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SITAGLIPTINA (JANUVIA) 25 MG TABLETA RECUBIERTA CAJA X 28</t>
+          <t>PREGABALINA 50MG CAP CX30 (LYRICA) - ASPEN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LYRICA 25MG X30</t>
+          <t>LYRICA 75MG X30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PREGABALINA (LYRICA) 25 MG CAPSULA CAJA X 30 - PFIZER</t>
+          <t>PREGABALINA 75 MG CAPSULA CAJA X 30 LYRICA 75MG (  LYRICA )</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LYRICA 50MG X30</t>
+          <t>LYRICA 75MG X14</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PREGABALINA 50MG CAP CX30 (LYRICA) - ASPEN</t>
+          <t>PREGABALINA75MG CAP CX14 (LYRICA) - ASPEN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LYRICA 75MG X30</t>
+          <t>LYRICA 150MG X30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PREGABALINA 75 MG CAPSULA CAJA X 30 LYRICA 75MG (  LYRICA )</t>
+          <t>PREGABALINA 150 MG CAPSULA CAJA X 30LYRICA 150MG ( ASPEN )</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LYRICA 75MG X14</t>
+          <t>LYRICA 300MG X30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PREGABALINA75MG CAP CX14 (LYRICA) - ASPEN</t>
+          <t>PREGABALINA 300 MG CAPSULA CAJA X 30 LYRICA 300MG ( ASPEN )</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>LYRICA 150MG X30</t>
+          <t>MYRBETRIC 25MG X30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PREGABALINA 150 MG CAPSULA CAJA X 30LYRICA 150MG ( ASPEN )</t>
+          <t>MIRABEGRON 25MG (MYRBETRIC) C*30 TAB LIB PRO - ASTELLAS</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LYRICA 300MG X30</t>
+          <t>MYRBETRIC 50MG X30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PREGABALINA 300 MG CAPSULA CAJA X 30 LYRICA 300MG ( ASPEN )</t>
+          <t>MIRABEGRON 50MG TAB LIB PRO CX30 (MYRBETRIC) - ASTELLAS</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MYRBETRIC 25MG X30</t>
+          <t>MYRBETRIC 50MG X60</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MIRABEGRON 25MG (MYRBETRIC) C*30 TAB LIB PRO - ASTELLAS</t>
+          <t>MIRABEGRON 50MG TAB LIB PRO CX60 (MYRBETRIC) - ASTELLAS</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MYRBETRIC 50MG X30</t>
+          <t>RYBELSUS 7MG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MIRABEGRON 50MG TAB LIB PRO CX30 (MYRBETRIC) - ASTELLAS</t>
+          <t>SEMAGLUTIDA 7MG TAB CX30 (RYBELSUS) - NOVO NORDISK</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MYRBETRIC 50MG X60</t>
+          <t>RYBELSUS 14MG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MIRABEGRON 50MG TAB LIB PRO CX60 (MYRBETRIC) - ASTELLAS</t>
+          <t>SEMAGLUTIDA 14MG TAB CX30 (RYBELSUS) - NOVO NORDISK</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RYBELSUS 7MG</t>
+          <t>RYBELSUS 3MG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SEMAGLUTIDA 7MG TAB CX30 (RYBELSUS) - NOVO NORDISK</t>
+          <t>SEMAGLUTIDA 3MG TAB CX30 (RYBELSUS) - NOVO NORDISK</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RYBELSUS 14MG</t>
+          <t>HIPERDEXT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SEMAGLUTIDA 14MG TAB CX30 (RYBELSUS) - NOVO NORDISK</t>
+          <t>TAMSULOSINA+DUTASTERIDA (HIPERDEXT) 0.4+0.5MGFCO*30 CAPSULA EXELTIS</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RYBELSUS 3MG</t>
+          <t>XIGDUO XR ROJA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SEMAGLUTIDA 3MG TAB CX30 (RYBELSUS) - NOVO NORDISK</t>
+          <t>DAPAGLIFLOZINA+METFORMINA 5MG+1000MGTAB LIB PRO CX56 (XIGDUO XR) - ASTRAZENECA</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HIPERDEXT</t>
+          <t>FYBOFORT PSYLLIUM 200G</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TAMSULOSINA+DUTASTERIDA (HIPERDEXT) 0.4+0.5MGFCO*30 CAPSULA EXELTIS</t>
+          <t>PSYLLIUM FIBRA NATURAL POL SUSP ORL PTEX200G (FYBOFORT) - NATURAL FHRESLY</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>XIGDUO XR ROJA</t>
+          <t>VERSATIS 1X5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DAPAGLIFLOZINA+METFORMINA 5MG+1000MGTAB LIB PRO CX56 (XIGDUO XR) - ASTRAZENECA</t>
+          <t>LIDOCAINA 700MG SIST TRANSD PARCH CAJA X5 (VERSATIS 5%) - GRUNENTHAL</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FYBOFORT PSYLLIUM 200G</t>
+          <t>VERSATIS 3X5</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PSYLLIUM FIBRA NATURAL POL SUSP ORL PTEX200G (FYBOFORT) - NATURAL FHRESLY</t>
+          <t>LIDOCAINA 700MG SIST TRANSD PARCH CAJAX15 (VERSATIS 5%) - GRUNENTHAL</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VERSATIS 1X5</t>
+          <t>VERSATIS 6X5</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LIDOCAINA 700MG SIST TRANSD PARCH CAJA X5 (VERSATIS 5%) - GRUNENTHAL</t>
+          <t>LIDOCAINA 700MG SIST TRANSD PARCH CAJAX30 (VERSATIS 5%) - GRUNENTHAL</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VERSATIS 3X5</t>
+          <t>ORENCIA 125MG/ML</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LIDOCAINA 700MG SIST TRANSD PARCH CAJAX15 (VERSATIS 5%) - GRUNENTHAL</t>
+          <t>ABATACEPT 125MG/ML SOL INY JERPREX1ML CX4 (ORENCIA) - BRISTOL</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VERSATIS 6X5</t>
+          <t>EYLIA 40MG/ML X1 JERINGA PRECARGADA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LIDOCAINA 700MG SIST TRANSD PARCH CAJAX30 (VERSATIS 5%) - GRUNENTHAL</t>
+          <t>AFLIBERCEPT 40MG/ML SOL INY INTRAVITREA JERPREX0.177ML CX1 (EYLIA) - BAYER</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ORENCIA 125MG/ML</t>
+          <t>GLUCOQUICK DIAMOND GD50 SISTEMA DE MONITOREO</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ABATACEPT 125MG/ML SOL INY JERPREX1ML CX4 (ORENCIA) - BRISTOL</t>
+          <t>EQUIPO GLUCOMETRO C*1(GLUCOQUICK GD50 BLUETHOOTH) - DIABETRICS</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EYLIA 40MG/ML X1 JERINGA PRECARGADA</t>
+          <t>ENTRESTO 50MG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AFLIBERCEPT 40MG/ML SOL INY INTRAVITREA JERPREX0.177ML CX1 (EYLIA) - BAYER</t>
+          <t>SACUBITRIL+VALSARTAN 50MG TAB CX30 (ENTRESTO) - NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GLUCOQUICK DIAMOND GD50 SISTEMA DE MONITOREO</t>
+          <t>ENTRESTO 100MG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EQUIPO GLUCOMETRO C*1(GLUCOQUICK GD50 BLUETHOOTH) - DIABETRICS</t>
+          <t>SACUBITRIL+VALSARTAN 100MG TAB CX60 (ENTRESTO) - NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ENTRESTO 50MG</t>
+          <t>ENTRESTO 200MG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SACUBITRIL+VALSARTAN 50MG TAB CX30 (ENTRESTO) - NOVARTIS</t>
+          <t>SACUBITRIL+VALSARTAN 200MG TAB CX60 (ENTRESTO) - NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ENTRESTO 100MG</t>
+          <t>ANORO</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SACUBITRIL+VALSARTAN 100MG TAB CX60 (ENTRESTO) - NOVARTIS</t>
+          <t>UMECLIDINIO+VILANTEROL 62.5MCG+25MCG (EQ.55MCG+22MCG) INH BUC FCOX30 DOSIS CX1 (ANORO ELLIPTA) - GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ENTRESTO 200MG</t>
+          <t>VOLTAREN EMULGEL 100G</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SACUBITRIL+VALSARTAN 200MG TAB CX60 (ENTRESTO) - NOVARTIS</t>
+          <t>DICLOFENACO DIETILAMINA 1.16 G(VOLTAREN EMULGEL) X 100G</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ANORO</t>
+          <t>VOLTAREN EMULGEL FORTE 100G</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>UMECLIDINIO+VILANTEROL 62.5MCG+25MCG (EQ.55MCG+22MCG) INH BUC FCOX30 DOSIS CX1 (ANORO ELLIPTA) - GLAXOSMITHKLINE</t>
+          <t>DICLOFENACO 2G/100G GEL TOP C*1 TUB X 100G (VOLTAREN FORTE 2.32%) - HALEON</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VOLTAREN EMULGEL 100G</t>
+          <t>SPIOLTO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DICLOFENACO DIETILAMINA 1.16 G(VOLTAREN EMULGEL) X 100G</t>
+          <t>TIOTROPIO + OLODATEROL (2.5 + 2.5)SOLUCION PARA INHALACION CAJA CON FRASCO X 60 APLICACIONES (SPIOLTO RESPIMAT) BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VOLTAREN EMULGEL FORTE 100G</t>
+          <t>SPIRIVA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DICLOFENACO 2G/100G GEL TOP C*1 TUB X 100G (VOLTAREN FORTE 2.32%) - HALEON</t>
+          <t>BROMURO DE TIOTROPIO 5MCG/DOSIS SOL INH CARTX30 DOSIS+INH CX1 (SPIRIVA RESPIMAT) - BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SPIOLTO</t>
+          <t>IMIGRAN FDT 50MG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TIOTROPIO + OLODATEROL (2.5 + 2.5)SOLUCION PARA INHALACION CAJA CON FRASCO X 60 APLICACIONES (SPIOLTO RESPIMAT) BOEHRINGER</t>
+          <t>SUMATRIPTAN 50MG TAB CX2 (IMIGRAN FDT) - GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SPIRIVA</t>
+          <t>GLYXAMBI AZUL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BROMURO DE TIOTROPIO 5MCG/DOSIS SOL INH CARTX30 DOSIS+INH CX1 (SPIRIVA RESPIMAT) - BOEHRINGER</t>
+          <t>EMPAGLIFLOZINA+LINAGLIPTINA10MG+5MG TAB CX30 (GLYXAMBI) - BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IMIGRAN FDT 50MG</t>
+          <t>GLYXAMBI ROSADA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SUMATRIPTAN 50MG TAB CX2 (IMIGRAN FDT) - GLAXOSMITHKLINE</t>
+          <t>EMPAGLIFLOZINA+LINAGLIPTINA25MG+5MG TAB CX30 (GLYXAMBI) - BOEHRINGER</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GLYXAMBI AZUL</t>
+          <t>RELVAR 100-25MCG X30</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA+LINAGLIPTINA10MG+5MG TAB CX30 (GLYXAMBI) - BOEHRINGER</t>
+          <t>FLUTICASONA FUROATO + VILANTEROL  (100+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR X 30 DOSIS POLVO PARA INHALACION BUCAL GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GLYXAMBI ROSADA</t>
+          <t>RELVAR 100-25MCG X30 DOSIS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EMPAGLIFLOZINA+LINAGLIPTINA25MG+5MG TAB CX30 (GLYXAMBI) - BOEHRINGER</t>
+          <t>FLUTICASONA FUROATO + VILANTEROL  (100+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR X 30 DOSIS POLVO PARA INHALACION BUCAL GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RELVAR 100-25MCG X30</t>
+          <t>RELVAR 200-25MCG X30</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FLUTICASONA FUROATO + VILANTEROL  (100+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR X 30 DOSIS POLVO PARA INHALACION BUCAL GLAXOSMITHKLINE</t>
+          <t>FLUTICASONA FUROATO + VILANTEROL (200+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR CON 30 DÓSIS POLVO PARA INHALACION GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RELVAR 100-25MCG X30 DOSIS</t>
+          <t>RELVAR 200-25MCG X30 DOSIS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FLUTICASONA FUROATO + VILANTEROL  (100+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR X 30 DOSIS POLVO PARA INHALACION BUCAL GLAXOSMITHKLINE</t>
+          <t>FLUTICASONA FUROATO + VILANTEROL (200+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR CON 30 DÓSIS POLVO PARA INHALACION GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RELVAR 200-25MCG X30</t>
+          <t>FANTER 10MG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FLUTICASONA FUROATO + VILANTEROL (200+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR CON 30 DÓSIS POLVO PARA INHALACION GLAXOSMITHKLINE</t>
+          <t>DAPAGLIFOZINA 10MG CX30 TAB (FANTER) ADIUM</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RELVAR 200-25MCG X30 DOSIS</t>
+          <t>SYNAGIS AZUL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FLUTICASONA FUROATO + VILANTEROL (200+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR CON 30 DÓSIS POLVO PARA INHALACION GLAXOSMITHKLINE</t>
+          <t>PALIVIZUMAB 100 MG/1ML SOLUCIÓN INYECTABLE  CAJA X VIAL SYNAGIS 100MG ASTRAZENECA</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FANTER 10MG</t>
+          <t>SYNAGIS ROSADA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DAPAGLIFOZINA 10MG CX30 TAB (FANTER) ADIUM</t>
+          <t>PALIVIZUMAB 50MG/0.5ML SOL INY VIALX0.5ML CX1 (SYNAGIS) - ASTRAZENECA</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SYNAGIS AZUL</t>
+          <t>MIRCERA 150MCG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PALIVIZUMAB 100 MG/1ML SOLUCIÓN INYECTABLE  CAJA X VIAL SYNAGIS 100MG ASTRAZENECA</t>
+          <t>METOXIPOLIETILENGLICOL-EPOETINA BETA 150MCG/0.3ML SOL INY JERPREX0.3ML CX1 (MIRCERA) - ROCHE</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SYNAGIS ROSADA</t>
+          <t>GALVUS MET 850MG X28</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PALIVIZUMAB 50MG/0.5ML SOL INY VIALX0.5ML CX1 (SYNAGIS) - ASTRAZENECA</t>
+          <t>METFORMINA+VILDAGLIPTINA 850MG+50MG TAB CX28 (GALVUS MET) - NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MIRCERA 150MCG</t>
+          <t>GALVUS MET 850MG X56</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>METOXIPOLIETILENGLICOL-EPOETINA BETA 150MCG/0.3ML SOL INY JERPREX0.3ML CX1 (MIRCERA) - ROCHE</t>
+          <t>VILDAGLIPTINA + METFORMINA (50+850) MG(GALVUS MET) CAJA X 56 COMPRIMIDO RECUBIERTO SIEGFRIED</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GALVUS MET 850MG X28</t>
+          <t>GALVUS MET 1000MG X28</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>METFORMINA+VILDAGLIPTINA 850MG+50MG TAB CX28 (GALVUS MET) - NOVARTIS</t>
+          <t>METFORMINA+VILDAGLIPTINA 1000MG+50MG TAB CX28 (GALVUS MET) - NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GALVUS MET 850MG X56</t>
+          <t>GALVUS MET 1000MG X56</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VILDAGLIPTINA + METFORMINA (50+850) MG(GALVUS MET) CAJA X 56 COMPRIMIDO RECUBIERTO SIEGFRIED</t>
+          <t>METFORMINA+VILDAGLIPTINA 1000MG+50MG C*56 TAB (GALVUS MET) - NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GALVUS MET 1000MG X28</t>
+          <t>GALVUS MET 500MG X28</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>METFORMINA+VILDAGLIPTINA 1000MG+50MG TAB CX28 (GALVUS MET) - NOVARTIS</t>
+          <t>METFORMINA+VILDAGLIPTINA 500MG+50MG  (GALVUS MET) C*28 TAB- NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GALVUS MET 1000MG X56</t>
+          <t>TEROVAN 100MG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>METFORMINA+VILDAGLIPTINA 1000MG+50MG C*56 TAB (GALVUS MET) - NOVARTIS</t>
+          <t>SACUBITRIL+VALSARTAN 100MG TAB (TEROVAN) CX60- ASOFARMA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GALVUS MET 500MG X28</t>
+          <t>TEROVAN 50MG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>METFORMINA+VILDAGLIPTINA 500MG+50MG  (GALVUS MET) C*28 TAB- NOVARTIS</t>
+          <t>SACUBITRIL+VALSARTAN 50MG TAB CX30 (TEROVAN) - ASOFARMA</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TEROVAN 100MG</t>
+          <t>TEROVAN 200MG</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SACUBITRIL+VALSARTAN 100MG TAB (TEROVAN) CX60- ASOFARMA</t>
+          <t>SACUBITRIL+VALSARTAN200MG TAB CX60 (TEROVAN) - ASOFARMA</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TEROVAN 50MG</t>
+          <t>ELIQUIS 5MG</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SACUBITRIL+VALSARTAN 50MG TAB CX30 (TEROVAN) - ASOFARMA</t>
+          <t>APIXABAN 5MG TAB CX60 (ELIQUIS) - PFIZER</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TEROVAN 200MG</t>
+          <t>ELIQUIS 2.5MG</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SACUBITRIL+VALSARTAN200MG TAB CX60 (TEROVAN) - ASOFARMA</t>
+          <t>APIXABAN 2.5MG TAB CX60 (ELIQUIS) - PFIZER</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ELIQUIS 5MG</t>
+          <t>JANUMET 1000MG X56</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>APIXABAN 5MG TAB CX60 (ELIQUIS) - PFIZER</t>
+          <t>METFORMINA+SITAGLIPTINA 1000MG+50MG TAB CX56 (JANUMET) - MSD</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ELIQUIS 2.5MG</t>
+          <t>JANUMET 1000MG X28</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>APIXABAN 2.5MG TAB CX60 (ELIQUIS) - PFIZER</t>
+          <t>SITAGLIPTINA 50MG+METFORMINA 1000MG(JANUMET) CAJA x28TAB REC.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>JANUMET 1000MG X56</t>
+          <t>JANUMET 850MG X56</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>METFORMINA+SITAGLIPTINA 1000MG+50MG TAB CX56 (JANUMET) - MSD</t>
+          <t>METFORMINA+SITAGLIPTINA 850MG+50MG TAB CX56 (JANUMET) - MSD</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JANUMET 1000MG X28</t>
+          <t>JANUMET 850MG X28</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SITAGLIPTINA 50MG+METFORMINA 1000MG(JANUMET) CAJA x28TAB REC.</t>
+          <t>SITAGLIPTINA + METFORMINA (50+850) MG (JANUMET) TABLETA RECUBIERTA CAJA X 28</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>JANUMET 850MG X56</t>
+          <t>VIMPAT 200MG X28</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>METFORMINA+SITAGLIPTINA 850MG+50MG TAB CX56 (JANUMET) - MSD</t>
+          <t>LACOSAMIDA 200MG C*28 TAB (VIMPAT) - UCB PHARMA S.A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>JANUMET 850MG X28</t>
+          <t>VIMPAT 100MG X28</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SITAGLIPTINA + METFORMINA (50+850) MG (JANUMET) TABLETA RECUBIERTA CAJA X 28</t>
+          <t>LACOSAMIDA 100MG TAB CX28 (VIMPAT) - UCB PHARMA S.A.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VIMPAT 200MG X28</t>
+          <t>VIMPAT 50MG X14</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LACOSAMIDA 200MG C*28 TAB (VIMPAT) - UCB PHARMA S.A.</t>
+          <t>LACOSAMIDA .50MG TAB CX14 (VIMPAT) - UCB PHARMA S.A</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VIMPAT 100MG X28</t>
+          <t>FENOVAS 20MG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LACOSAMIDA 100MG TAB CX28 (VIMPAT) - UCB PHARMA S.A.</t>
+          <t>ACIDO FENOFIBRICO+ROSUVASTATINA135MG+20MG CAP CX30 (FENOVAS) - PROCAPS</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>VIMPAT 50MG X14</t>
+          <t>FENOVAS 10MG</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LACOSAMIDA .50MG TAB CX14 (VIMPAT) - UCB PHARMA S.A</t>
+          <t>ACIDO FENOFIBRICO+ROSUVASTATINA 135MG+10MG CAP CX30 (FENOVAS) - PROCAPS</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FENOVAS 20MG</t>
+          <t>VIMPAT 10MG/ML SOLUCION ORAL 200ML</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ACIDO FENOFIBRICO+ROSUVASTATINA135MG+20MG CAP CX30 (FENOVAS) - PROCAPS</t>
+          <t>LACOSAMIDA    10 MG/ML (VIMPAT ®)  SOLUCION ORAL</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FENOVAS 10MG</t>
+          <t>DEPAKENE 250MG/5ML</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ACIDO FENOFIBRICO+ROSUVASTATINA 135MG+10MG CAP CX30 (FENOVAS) - PROCAPS</t>
+          <t>ACIDO VALPROICO 250MG/5ML (5%) JBE C*1 FCO X 120ML (DEPAKENE) - LAFRANCOL</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>VIMPAT 10MG/ML SOLUCION ORAL 200ML</t>
+          <t>Metaspray 0.05% X100 Aplicaciones 10Ml</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LACOSAMIDA    10 MG/ML (VIMPAT ®)  SOLUCION ORAL</t>
+          <t>MOMETASONA  50MCG/DOSIS (0.05%) SUSP NAS C*1 FCO SPRAY 100 PULS (10G) (METASPRAY 10G) - NOVAMED</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DEPAKENE 250MG/5ML</t>
+          <t>Keixa 5Mg X60</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ACIDO VALPROICO 250MG/5ML (5%) JBE C*1 FCO X 120ML (DEPAKENE) - LAFRANCOL</t>
+          <t>APIXABAN (KEIXA) 5 MG TABL RECUBIERTA</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Metaspray 0.05% X100 Aplicaciones 10Ml</t>
+          <t>Epnone 25Mg X30</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MOMETASONA  50MCG/DOSIS (0.05%) SUSP NAS C*1 FCO SPRAY 100 PULS (10G) (METASPRAY 10G) - NOVAMED</t>
+          <t>EPLERENONA(EPNONE) 25 MG CAJA X 30 TBL REC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Keixa 5Mg X60</t>
+          <t>Farmalax Polvo Para Reconstituir 160G</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>APIXABAN (KEIXA) 5 MG TABL RECUBIERTA</t>
+          <t>POLIETILENGLICOL 3350 100G/100G (100%) POL ORL FCOX160G CX1 (FARMALAX) - ECAR</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Epnone 25Mg X30</t>
+          <t>Epibalin 150Mg X30</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EPLERENONA(EPNONE) 25 MG CAJA X 30 TBL REC</t>
+          <t>PREGABALINA 150 MG CAPSULA DURA  CAJA X 30EPIBALIN 150MG ( MSN LABORATORIES PRIVATED LIMITED )</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Farmalax Polvo Para Reconstituir 160G</t>
+          <t>Rosuvina 40 x30</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>POLIETILENGLICOL 3350 100G/100G (100%) POL ORL FCOX160G CX1 (FARMALAX) - ECAR</t>
+          <t>ROSUVASTATINA 40MG C*30 TAB (ROSUVINA 40) LEGRAND</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Epibalin 150Mg X30</t>
+          <t>Nodol Plus 325/5Mg X100</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PREGABALINA 150 MG CAPSULA DURA  CAJA X 30EPIBALIN 150MG ( MSN LABORATORIES PRIVATED LIMITED )</t>
+          <t>ACETAMINOFEN+HIDROCODONA BITARTRATO 325MG+5MG TAB CX100 (NODOL PLUS) - SALUS PHARMA</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Rosuvina 40 x30</t>
+          <t>Encefabol 600Mg X10 Grageas</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ROSUVASTATINA 40MG C*30 TAB (ROSUVINA 40) LEGRAND</t>
+          <t>PIRITINOL DICLORHIDRATO MONOHIDRATO	600 MG C* 10 GRAGEAS. (ENCEFABOL) MERCK S.A.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Nodol Plus 325/5Mg X100</t>
+          <t>Prograf 1Mg</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ACETAMINOFEN+HIDROCODONA BITARTRATO 325MG+5MG TAB CX100 (NODOL PLUS) - SALUS PHARMA</t>
+          <t>TACROLIMUS 1MG CAP CX50 (PROGRAF) - ASTELLAS</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Encefabol 600Mg X10 Grageas</t>
+          <t>Cialis X8</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PIRITINOL DICLORHIDRATO MONOHIDRATO	600 MG C* 10 GRAGEAS. (ENCEFABOL) MERCK S.A.</t>
+          <t>TADALAFIL 20 MG COMPRIMIDO RECUBIERTO(CIALIS) CAJA X 8 LILLY</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Prograf 1Mg</t>
+          <t>Mycotas 360Mg Acido Micofenolico</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TACROLIMUS 1MG CAP CX50 (PROGRAF) - ASTELLAS</t>
+          <t>MICOFENOLATO SODICO 360MG TAB LIB RET CX120 (MYCOTAS) - INTAS PHARMACEUTICALS</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Cialis X8</t>
+          <t>Etox 90Mg X14</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TADALAFIL 20 MG COMPRIMIDO RECUBIERTO(CIALIS) CAJA X 8 LILLY</t>
+          <t>ETORICOXIB 90 MG TABLETA RECUBIERTA(ETOX) CAJA X 14 EUROFARMA DE COLOMBIA</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Mycotas 360Mg Acido Micofenolico</t>
+          <t>Vilzer 50Mg X30</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MICOFENOLATO SODICO 360MG TAB LIB RET CX120 (MYCOTAS) - INTAS PHARMACEUTICALS</t>
+          <t>VILDAGLIPTINA 50 MG TABLETAS DE LIBERACION  (VILZER) TABLETA 1U / CAJA X 30</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Etox 90Mg X14</t>
+          <t>Constilax X12 Satchets</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ETORICOXIB 90 MG TABLETA RECUBIERTA(ETOX) CAJA X 14 EUROFARMA DE COLOMBIA</t>
+          <t>LACTULOSA 66.7G/100ML SOL ORL SOBX15ML CX12 (CONSTILAX) - HUMAX</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Vilzer 50Mg X30</t>
+          <t>Ceumid 500Mg X30</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>VILDAGLIPTINA 50 MG TABLETAS DE LIBERACION  (VILZER) TABLETA 1U / CAJA X 30</t>
+          <t>LEVETIRACETAM  (CEUMID) 500 MG CAJAJ X 30 COMPRIMIDOS RECU - MEGALABS</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Constilax X12 Satchets</t>
+          <t>Balance Forte 325/65Mg X30</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>LACTULOSA 66.7G/100ML SOL ORL SOBX15ML CX12 (CONSTILAX) - HUMAX</t>
+          <t>ACETAMINOFEN+CAFEINA 325MG+65MG TAB CX30 (BALANCEFORTE) - BALANCE PHARMA</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ceumid 500Mg X30</t>
+          <t>Colmibe 20/10Mg X30</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LEVETIRACETAM  (CEUMID) 500 MG CAJAJ X 30 COMPRIMIDOS RECU - MEGALABS</t>
+          <t>ATORVASTATINA+EZETIMIBE 20MG+10MG C*30 TAB (COLMIBE) - FARMACEUTICA PARAGUAYA</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Balance Forte 325/65Mg X30</t>
+          <t>Coveram 5/5Mg X30</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ACETAMINOFEN+CAFEINA 325MG+65MG TAB CX30 (BALANCEFORTE) - BALANCE PHARMA</t>
+          <t>AMLODIPINO+PERINDOPRIL ARGININA 5MG+5MG C*1 FCO X 30 TAB (COVERAM) - SERVIER</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Colmibe 20/10Mg X30</t>
+          <t>Daivobet Gel 0.05/0.5Mg/G 30G</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ATORVASTATINA+EZETIMIBE 20MG+10MG C*30 TAB (COLMIBE) - FARMACEUTICA PARAGUAYA</t>
+          <t>BETAMETASONA+CALCIPOTRIOL (0.5MG+0.05MG)/100G GEL TOP TUBX30G CX1 (DAIVOBET) - LEO PHARMA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Coveram 5/5Mg X30</t>
+          <t>Inflaxen 20Mg X30</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AMLODIPINO+PERINDOPRIL ARGININA 5MG+5MG C*1 FCO X 30 TAB (COVERAM) - SERVIER</t>
+          <t>LEFLUNOMIDA 20 MG CAPSULA BLANDA(INFLAXEN) CAJA X 30</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Daivobet Gel 0.05/0.5Mg/G 30G</t>
+          <t>Pantocal 40Mg X28</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BETAMETASONA+CALCIPOTRIOL (0.5MG+0.05MG)/100G GEL TOP TUBX30G CX1 (DAIVOBET) - LEO PHARMA</t>
+          <t>PANTOPRAZOL 40 MG (PANTOCAL) TABLETA DE LIBERACIÓN RETARDADA CAJA *28</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Inflaxen 20Mg X30</t>
+          <t>Pentasa 1G X14</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LEFLUNOMIDA 20 MG CAPSULA BLANDA(INFLAXEN) CAJA X 30</t>
+          <t>MESALAZINA/MESALAZINE 1MGC*14 UNDS (PENTASA) FERRING</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Pantocal 40Mg X28</t>
+          <t>Clexane 40Mg X10</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PANTOPRAZOL 40 MG (PANTOCAL) TABLETA DE LIBERACIÓN RETARDADA CAJA *28</t>
+          <t>ENOXAPARINA SODICA (CLEXANE) 40 MG/0.4 ML SOLUCION INYECTABLE  CAJA X 10 JERINGAS PRELLENADAS  - SANOFI</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Pentasa 1G X14</t>
+          <t>Clexane 40mg</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MESALAZINA/MESALAZINE 1MGC*14 UNDS (PENTASA) FERRING</t>
+          <t>ENOXAPARINA SODICA (CLEXANE) 40 MG/0.4 ML SOLUCION INYECTABLE  CAJA X 10 JERINGAS PRELLENADAS  - SANOFI</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Clexane 40Mg X10</t>
+          <t>Aciclovir 800Mg X10</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ENOXAPARINA SODICA (CLEXANE) 40 MG/0.4 ML SOLUCION INYECTABLE  CAJA X 10 JERINGAS PRELLENADAS  - SANOFI</t>
+          <t>ACICLOVIR 800MG CAJA*10 TABLETAGENFAR</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Clexane 40mg</t>
+          <t>Optive 15Ml</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ENOXAPARINA SODICA (CLEXANE) 40 MG/0.4 ML SOLUCION INYECTABLE  CAJA X 10 JERINGAS PRELLENADAS  - SANOFI</t>
+          <t>CARBOXIMETILCELULOSA+GLICERINA (5MG+9MG)/ML (0.5%+0.9%) SOL OFT GTS FCOX15ML CX1 (OPTIVE) - ABBVIE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Aciclovir 800Mg X10</t>
+          <t>Caltrate X30</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ACICLOVIR 800MG CAJA*10 TABLETAGENFAR</t>
+          <t>CALCIO+VITAMINA D 600MG+400UI TAB FCOX30 CX1 (CALTRATE 600 + D) - HALEON</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Optive 15Ml</t>
+          <t>Cialis X2</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CARBOXIMETILCELULOSA+GLICERINA (5MG+9MG)/ML (0.5%+0.9%) SOL OFT GTS FCOX15ML CX1 (OPTIVE) - ABBVIE</t>
+          <t>TADALAFILO20MG C*2 TAB (CIALIS) - ELI LILLY</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Caltrate X30</t>
+          <t>Babyderm 500G</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CALCIO+VITAMINA D 600MG+400UI TAB FCOX30 CX1 (CALTRATE 600 + D) - HALEON</t>
+          <t>UNGUENTO BABY DERM POTE 500GRAMOSC</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Cialis X2</t>
+          <t>Cialis X4</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TADALAFILO20MG C*2 TAB (CIALIS) - ELI LILLY</t>
+          <t>TADALAFILO 20MG C*4 TAB (CIALIS) - ELI LILLY</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Babyderm 500G</t>
+          <t>Seroxat Clorhidrato De Paroxetina 25Mg 10 Tabletas</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>UNGUENTO BABY DERM POTE 500GRAMOSC</t>
+          <t>PAROXETINA 25MG  (SEROXAT CR) TAB LIB CONT CX10- GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Cialis X4</t>
+          <t>Cialis X1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TADALAFILO 20MG C*4 TAB (CIALIS) - ELI LILLY</t>
+          <t>TADALAFILO20MG C*1 TAB (CIALIS) - ELI LILLY</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Seroxat Clorhidrato De Paroxetina 25Mg 10 Tabletas</t>
+          <t>Nepro Bp 237Ml</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PAROXETINA 25MG  (SEROXAT CR) TAB LIB CONT CX10- GLAXOSMITHKLINE</t>
+          <t>NEPRO BP - ALIMENTO ESPECIAL POLIMERICO HIPERCALORICO 1.8KCAL/ML SOL ORL LTAX237ML (VAINILLA) - ABBOTT</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Cialis X1</t>
+          <t>Neupro 8Mg/24H</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TADALAFILO20MG C*1 TAB (CIALIS) - ELI LILLY</t>
+          <t>ROTIGOTINA (8 MG/24H)(NEUPRO) SISTEMAS TRANSDERMICO CAJA X 14 PARCHES TRASDERMICO BIOPAS</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Nepro Bp 237Ml</t>
+          <t>Neupro Azul</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>NEPRO BP - ALIMENTO ESPECIAL POLIMERICO HIPERCALORICO 1.8KCAL/ML SOL ORL LTAX237ML (VAINILLA) - ABBOTT</t>
+          <t>ROTIGOTINA (8 MG/24H)(NEUPRO) SISTEMAS TRANSDERMICO CAJA X 14 PARCHES TRASDERMICO BIOPAS</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Neupro 8Mg/24H</t>
+          <t>Mitrul 15Mg X10</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ROTIGOTINA (8 MG/24H)(NEUPRO) SISTEMAS TRANSDERMICO CAJA X 14 PARCHES TRASDERMICO BIOPAS</t>
+          <t>CICLOBENZAPRINA 15MG CAP LIB PRO CX10 (MITRUL) - ADARE PHARMACEUTICALS</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Neupro Azul</t>
+          <t>Seretide Diskus 50/100Mcg X60</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ROTIGOTINA (8 MG/24H)(NEUPRO) SISTEMAS TRANSDERMICO CAJA X 14 PARCHES TRASDERMICO BIOPAS</t>
+          <t>SALMETEROL + FLUTICASONA (50+100) MCG (SERETIDE DISKUS) CAJA X 1 INHALADOR X 60 DOSISPOLVO PARA INHALACION BUCAL GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Mitrul 15Mg X10</t>
+          <t>Seretide Diskus 50/250Mcg X60</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CICLOBENZAPRINA 15MG CAP LIB PRO CX10 (MITRUL) - ADARE PHARMACEUTICALS</t>
+          <t>PROPIONATO FLUTICASONA+SALMETEROL (250MCG+50MCG)/DOSIS POL INH FCO*60DOSIS (SERETIDE DISKUS) - GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Seretide Diskus 50/100Mcg X60</t>
+          <t>Seretide Diskus 50/500Mcg X60</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SALMETEROL + FLUTICASONA (50+100) MCG (SERETIDE DISKUS) CAJA X 1 INHALADOR X 60 DOSISPOLVO PARA INHALACION BUCAL GLAXOSMITHKLINE</t>
+          <t>PROPIONATO FLUTICASONA+SALMETEROL (500MCG+50MCG)/DOSIS POL INH C*1 FCO X 60 DOSIS (SERETIDE DISKUS) - GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Seretide Diskus 50/250Mcg X60</t>
+          <t>Sitagliptina Genfar 100Mg X30</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PROPIONATO FLUTICASONA+SALMETEROL (250MCG+50MCG)/DOSIS POL INH FCO*60DOSIS (SERETIDE DISKUS) - GLAXOSMITHKLINE</t>
+          <t>SITAGLIPTINA100 MG CX30 TAB GENFAR</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Seretide Diskus 50/500Mcg X60</t>
+          <t>Simponi 50Mg</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PROPIONATO FLUTICASONA+SALMETEROL (500MCG+50MCG)/DOSIS POL INH C*1 FCO X 60 DOSIS (SERETIDE DISKUS) - GLAXOSMITHKLINE</t>
+          <t>GOLIMUMAB 50 MG/0.5 ML SOLUCION INYECTABLECAJA X 1 PLUMA PRECARGADA X 0.5 ML ( SIMPONI ) JANSSEN</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Sitagliptina Genfar 100Mg X30</t>
+          <t>Suganon Evogliptina 5Mg X30</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SITAGLIPTINA100 MG CX30 TAB GENFAR</t>
+          <t>EVOGLIPTINA 5MG (SUGANON) C*30 TAB EUROFARNA</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Simponi 50Mg</t>
+          <t>Tadalafilo 5Mg X28 Genfar</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>GOLIMUMAB 50 MG/0.5 ML SOLUCION INYECTABLECAJA X 1 PLUMA PRECARGADA X 0.5 ML ( SIMPONI ) JANSSEN</t>
+          <t>TADALAFILO 5MG C*28 TAB - GENFAR</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Suganon Evogliptina 5Mg X30</t>
+          <t>Trileptal Oxcarbazepina 300Mg X30</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EVOGLIPTINA 5MG (SUGANON) C*30 TAB EUROFARNA</t>
+          <t>OXCARBAZEPINA 300MG C*30 TAB (TRILEPTAL) - NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Tadalafilo 5Mg X28 Genfar</t>
+          <t>Galvus Met 50/1000Mg X56</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>TADALAFILO 5MG C*28 TAB - GENFAR</t>
+          <t>METFORMINA+VILDAGLIPTINA 1000MG+50MG C*56 TAB (GALVUS MET) - NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Trileptal Oxcarbazepina 300Mg X30</t>
+          <t>Avodart 0.5Mg X30</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>OXCARBAZEPINA 300MG C*30 TAB (TRILEPTAL) - NOVARTIS</t>
+          <t>DUTASTERIDA 0.5MG C*30 CAP (AVODART) - GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Galvus Met 50/1000Mg X56</t>
+          <t>Balandof 7.5/325Mg X30</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>METFORMINA+VILDAGLIPTINA 1000MG+50MG C*56 TAB (GALVUS MET) - NOVARTIS</t>
+          <t>ACETAMINOFEN+HIDROCODONA BITARTRATO 325MG+7.5MG TAB CX30 (BALANDOF) - BALANCE PHARMA</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Avodart 0.5Mg X30</t>
+          <t>Biocalcium D X30</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DUTASTERIDA 0.5MG C*30 CAP (AVODART) - GLAXOSMITHKLINE</t>
+          <t>CARBONATO DE CALCIO+VITAMINA D3(BIOCALCIUM D ) 500MG+200UI CAJA X 30 SOBRES</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Balandof 7.5/325Mg X30</t>
+          <t>Xigduo Xr Amarilla</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ACETAMINOFEN+HIDROCODONA BITARTRATO 325MG+7.5MG TAB CX30 (BALANDOF) - BALANCE PHARMA</t>
+          <t>DAPAGLIFLOZINA+METFORMINA 10MG+1000MGTAB LIB PRO CX28 (XIGDUO XR) - ASTRAZENECA</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Biocalcium D X30</t>
+          <t>Xultophy Caja X1</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CARBONATO DE CALCIO+VITAMINA D3(BIOCALCIUM D ) 500MG+200UI CAJA X 30 SOBRES</t>
+          <t>INSULINA DEGLUDEC + LIRAGLUTIDA (100UI+3.6MG) /ML SOLUCION INYECTABLE  CAJA X 1 PEN X 3 ML(XULTOPHY®) NOVONORDISK</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Xigduo Xr Amarilla</t>
+          <t>Valatril 24/26Mg X30</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DAPAGLIFLOZINA+METFORMINA 10MG+1000MGTAB LIB PRO CX28 (XIGDUO XR) - ASTRAZENECA</t>
+          <t>SACUBITRILO + VALSARTAN 24MG+26MG TAB RECUB CAJA * 30 (VALATRIL) HETERO</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Xultophy Caja X1</t>
+          <t>Dapazin 10Mg X30</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>INSULINA DEGLUDEC + LIRAGLUTIDA (100UI+3.6MG) /ML SOLUCION INYECTABLE  CAJA X 1 PEN X 3 ML(XULTOPHY®) NOVONORDISK</t>
+          <t>DAPAGLIFLOZINA 10 MGCAJA X 30 TABLETAS (DAPAZIN) GENBIE SAS</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Valatril 24/26Mg X30</t>
+          <t>Darunavir 800 Mg + Ritonavir 100 Mg</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SACUBITRILO + VALSARTAN 24MG+26MG TAB RECUB CAJA * 30 (VALATRIL) HETERO</t>
+          <t>ETEVIHR® RDARUNAVIR ETANOLATO EQUIVALENTE A DARUNAVIR A 800mg; RITONAVIR A 100mg CAJA X 30</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Dapazin 10Mg X30</t>
+          <t>Daflon 1000Mg Satchets X30</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>DAPAGLIFLOZINA 10 MGCAJA X 30 TABLETAS (DAPAZIN) GENBIE SAS</t>
+          <t>DIOSMINA+HESPERIDINA (900MG+100MG)10ML SUSP ORL SACHETSX10ML CX30 (DAFLON) - SERVIER</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Darunavir 800 Mg + Ritonavir 100 Mg</t>
+          <t>Mabthera 500Mg/50Ml</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ETEVIHR® RDARUNAVIR ETANOLATO EQUIVALENTE A DARUNAVIR A 800mg; RITONAVIR A 100mg CAJA X 30</t>
+          <t>RITUXIMAB 500 MG/50ML (MABTHERA) CAJA X 1 VIAL SOLUCIÓN INYECTABLE ROCHE</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Daflon 1000Mg Satchets X30</t>
+          <t>Prolia 60Mg/Ml</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DIOSMINA+HESPERIDINA (900MG+100MG)10ML SUSP ORL SACHETSX10ML CX30 (DAFLON) - SERVIER</t>
+          <t>DENOSUMAB 60 MG/ML SOLUCIÓN INYECTABLE CAJA X 1 JERINGA PRELLENADA (PROLIA) - AMGEN BIOTECNOLOGICA S.A.S</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Mabthera 500Mg/50Ml</t>
+          <t>Exforgehct 10/320/25Mg X28</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RITUXIMAB 500 MG/50ML (MABTHERA) CAJA X 1 VIAL SOLUCIÓN INYECTABLE ROCHE</t>
+          <t>AMLODIPINO+HIDROCLOROTIAZIDA+VALSARTAN 10MG+25MG+320MG TAB CX28 (EXFORGE HCT) - NOVARTIS</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Prolia 60Mg/Ml</t>
+          <t>Fanter 10Mg X30</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DENOSUMAB 60 MG/ML SOLUCIÓN INYECTABLE CAJA X 1 JERINGA PRELLENADA (PROLIA) - AMGEN BIOTECNOLOGICA S.A.S</t>
+          <t>DAPAGLIFOZINA 10MG CX30 TAB (FANTER) ADIUM</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Exforgehct 10/320/25Mg X28</t>
+          <t>Neupro roja</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>AMLODIPINO+HIDROCLOROTIAZIDA+VALSARTAN 10MG+25MG+320MG TAB CX28 (EXFORGE HCT) - NOVARTIS</t>
+          <t>ROTIGOTINA 9MG (NEUPRO 4MG/24H) SIST TRANSD C*14 PARCH- UCB PHARMA S.A.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Fanter 10Mg X30</t>
+          <t>Neupro rojo</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DAPAGLIFOZINA 10MG CX30 TAB (FANTER) ADIUM</t>
+          <t>ROTIGOTINA 9MG (NEUPRO 4MG/24H) SIST TRANSD C*14 PARCH- UCB PHARMA S.A.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Neupro roja</t>
+          <t>Neupro 4Mg/24h</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -2879,216 +2879,288 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Neupro rojo</t>
+          <t>Clenox 80Mg X1</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ROTIGOTINA 9MG (NEUPRO 4MG/24H) SIST TRANSD C*14 PARCH- UCB PHARMA S.A.</t>
+          <t>ENOXAPARINA 80MG/0.8ML SOL INY JERPREX0.8ML CX1 (CLENOX) - PROCAPS</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Neupro 4Mg/24h</t>
+          <t>Vesomni 6Mg/0.4Mg X30</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ROTIGOTINA 9MG (NEUPRO 4MG/24H) SIST TRANSD C*14 PARCH- UCB PHARMA S.A.</t>
+          <t>SOLIFENACINA SUCCINATO+TAMSULOSINA 6MG+0.4MG TAB LIB PRO CX30 (VESOMNI) - ASTELLAS</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Clenox 80Mg X1</t>
+          <t>Venosmil X60 Capsulas</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ENOXAPARINA 80MG/0.8ML SOL INY JERPREX0.8ML CX1 (CLENOX) - PROCAPS</t>
+          <t>HIDROSMINA 200MG CAP CX60 (VENOSMIL) - FAES FARMA</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Vesomni 6Mg/0.4Mg X30</t>
+          <t>Muvett S 200/120Mg X21</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SOLIFENACINA SUCCINATO+TAMSULOSINA 6MG+0.4MG TAB LIB PRO CX30 (VESOMNI) - ASTELLAS</t>
+          <t>SIMETICONA+TRIMEBUTINA 120MG+200MG TAB CX21 (MUVETT S) - PROCAPS</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Venosmil X60 Capsulas</t>
+          <t>Pasta Lassar 100G</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HIDROSMINA 200MG CAP CX60 (VENOSMIL) - FAES FARMA</t>
+          <t>OXIDO DE ZINC PASTA LASSAR 25% CREMA TOPICAPOTE X 100 GRAMOS QUIFARMA</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Muvett S 200/120Mg X21</t>
+          <t>Lipotic 600Mg</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SIMETICONA+TRIMEBUTINA 120MG+200MG TAB CX21 (MUVETT S) - PROCAPS</t>
+          <t>TIOCTICO ACIDO 600 MG (LIPOTIC) FRASCO X 30 TABLETA RECUBIERTA</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Pasta Lassar 100G</t>
+          <t>Brivaxon 100Mg X30 Tecnofarma</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>OXIDO DE ZINC PASTA LASSAR 25% CREMA TOPICAPOTE X 100 GRAMOS QUIFARMA</t>
+          <t>BRIVARACETAM 100 MG TABLETA RECUBIERTA  CAJA X 30BRIVAXON 100MG (TECNOFARMA)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Lipotic 600Mg</t>
+          <t>Valatril 49/51Mg X60</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>TIOCTICO ACIDO 600 MG (LIPOTIC) FRASCO X 30 TABLETA RECUBIERTA</t>
+          <t>SACIUBITRIL+ VALSARTAN 49+51 CX60 TAB (VALATRIL) HETERO</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Brivaxon 100Mg X30 Tecnofarma</t>
+          <t>Relvar 100/25Mcg X30</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>BRIVARACETAM 100 MG TABLETA RECUBIERTA  CAJA X 30BRIVAXON 100MG (TECNOFARMA)</t>
+          <t>FLUTICASONA FUROATO + VILANTEROL  (100+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR X 30 DOSIS POLVO PARA INHALACION BUCAL GLAXOSMITHKLINE</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Valatril 49/51Mg X60</t>
+          <t>Invega Sustenna 150Mg</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SACIUBITRIL+ VALSARTAN 49+51 CX60 TAB (VALATRIL) HETERO</t>
+          <t>PALIPERIDONA 150MG SUSP INY LIB PRO JERPRE CX1 (INVEGA SUSTENNA) - JANSSEN</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Relvar 100/25Mcg X30</t>
+          <t>Biempag 25Mg X30</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FLUTICASONA FUROATO + VILANTEROL  (100+25) MCG(RELVAR ELLIPTA) CAJA X 1 INHALADOR X 30 DOSIS POLVO PARA INHALACION BUCAL GLAXOSMITHKLINE</t>
+          <t>ELTROMBOPAG 25 MGTABLETA RECUBIERTA SAS</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Invega Sustenna 150Mg</t>
+          <t>Dupixent 300Mg X2</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PALIPERIDONA 150MG SUSP INY LIB PRO JERPRE CX1 (INVEGA SUSTENNA) - JANSSEN</t>
+          <t>DUPILUMAB 300MG/2ML SOL INY JERPREX2ML CX2 (DUPIXENT) - SANOFI</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Biempag 25Mg X30</t>
+          <t>Eliquis 2.5Mg X60</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ELTROMBOPAG 25 MGTABLETA RECUBIERTA SAS</t>
+          <t>APIXABAN 2.5MG TAB CX60 (ELIQUIS) - PFIZER</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Dupixent 300Mg X2</t>
+          <t>Trulicity Amarilla</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>DUPILUMAB 300MG/2ML SOL INY JERPREX2ML CX2 (DUPIXENT) - SANOFI</t>
+          <t>DULAGLUTIDA 0.75MG/0,5ML SOL INYC*4 JERPRE X 0.5ML (TRULICITY) - ELI LILLY</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Eliquis 2.5Mg X60</t>
+          <t>Victoza Caja X1</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>APIXABAN 2.5MG TAB CX60 (ELIQUIS) - PFIZER</t>
+          <t>LIRAGLUTIDA 6MG/ML SOL INY JERPREX3ML CX1 (VICTOZA) - NOVO NORDISK</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Trulicity Amarilla</t>
+          <t>Victoza Lapiz</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DULAGLUTIDA 0.75MG/0,5ML SOL INYC*4 JERPRE X 0.5ML (TRULICITY) - ELI LILLY</t>
+          <t>LIRAGLUTIDA 6MG/ML SOL INY JERPREX3ML LAPICERO (VICTOZA) - NOVO NORDISK</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Victoza Caja X1</t>
+          <t>Delta 40Mg X10</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6MG/ML SOL INY JERPREX3ML CX1 (VICTOZA) - NOVO NORDISK</t>
+          <t>ENOXAPARINA SODICA (DELTA) 40 MG/0.4 ML CAJA X10 SOLUCION INYECTABLE</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Victoza Lapiz</t>
+          <t>Delta 60Mg X10</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>LIRAGLUTIDA 6MG/ML SOL INY JERPREX3ML LAPICERO (VICTOZA) - NOVO NORDISK</t>
+          <t>ENOXAPARINA 60MG/0.6ML SOL INY JERPREX0.6ML CX10 - DELTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ROSUVINA 10/40 X30</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>EZETIMIBA+ROSUVASTATINA 10MG+40MG TAB CX30 (ROSUVINA E) - LEGRAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Soliqua 10/40 Caja X1</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>INSULINA GLARGINA+LIXISENATIDA (100UI+50MCG)/ML SOL INY C*1 PEN X 3ML (SOLIQUA 10-40) - SANOFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Soliqua 10/40 Lapiz</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>INSULINA GLARGINA+LIXISENATIDA (100UI+50MCG)/ML SOL INY C*1 LAPICERO X 3ML (SOLIQUA 10-40) - SANOFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Soliqua 30/60 Caja X1</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>INSULINA GLARGINA+LIXISENATIDA (100UI+33MCG)/ML SOL INY C*1 PEN X 3ML (SOLIQUA 30-60) - SANOFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Soliqua 30/60 Lapiz</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>INSULINA GLARGINA+LIXISENATIDA (100UI+33MCG)/ML SOL INY LAPICERO X 3ML (SOLIQUA 30-60) - SANOFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Xalutem 2.5Mg X30</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>APIXABAN 2,5MG(XALUTEM ®)TAB CX30 CYH</t>
         </is>
       </c>
     </row>
